--- a/data/trans_camb/IP19C04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,68; 2,61</t>
+          <t>-7,64; 2,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 8,52</t>
+          <t>-5,62; 8,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 8,42</t>
+          <t>-3,67; 8,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 8,05</t>
+          <t>-6,44; 7,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,26; -1,37</t>
+          <t>-11,62; -1,38</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 1,76</t>
+          <t>-9,27; 1,77</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,72; 3,01</t>
+          <t>-5,56; 2,72</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,38; 1,49</t>
+          <t>-6,71; 1,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 3,15</t>
+          <t>-4,34; 3,34</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-65,12; —</t>
+          <t>-62,81; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-86,73; 232,96</t>
+          <t>-87,44; 166,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 198,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-71,53; 184,48</t>
+          <t>-69,62; 195,39</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-11,97; 3,03</t>
+          <t>-12,12; 3,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 1,22</t>
+          <t>-14,3; 0,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,18; 0,09</t>
+          <t>-13,54; 0,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-15,35; -1,75</t>
+          <t>-16,01; -1,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 5,21</t>
+          <t>-10,66; 5,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,12; 1,54</t>
+          <t>-12,89; 1,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-10,76; -0,37</t>
+          <t>-11,25; -0,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 1,6</t>
+          <t>-8,99; 1,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,18; -0,09</t>
+          <t>-10,4; -0,6</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,15</t>
+          <t>-100,0; 32,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,66; 79,22</t>
+          <t>-89,67; 83,97</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-94,29; 10,22</t>
+          <t>-93,56; 12,72</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,38; -1,84</t>
+          <t>-16,67; -1,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 16,99</t>
+          <t>-4,42; 17,29</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 4,03</t>
+          <t>-12,33; 3,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,93; 9,16</t>
+          <t>-8,26; 8,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 4,72</t>
+          <t>-9,51; 4,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 11,34</t>
+          <t>-7,66; 12,0</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 1,73</t>
+          <t>-9,22; 1,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 7,39</t>
+          <t>-6,15; 7,58</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 5,47</t>
+          <t>-7,37; 5,68</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-79,6; —</t>
+          <t>-76,47; 895,28</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-81,55; 414,08</t>
+          <t>-85,35; 345,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 298,27</t>
+          <t>-100,0; 340,19</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 547,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-88,24; 155,51</t>
+          <t>-91,91; 68,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-65,12; 219,02</t>
+          <t>-70,54; 249,81</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,47; 191,97</t>
+          <t>-84,4; 187,5</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 8,91</t>
+          <t>-3,41; 8,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 4,38</t>
+          <t>-6,48; 4,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 3,47</t>
+          <t>-6,57; 3,76</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; 6,92</t>
+          <t>-5,02; 7,1</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 2,47</t>
+          <t>-7,99; 2,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,54; 3,05</t>
+          <t>-7,36; 2,61</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 5,96</t>
+          <t>-2,83; 6,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 2,27</t>
+          <t>-5,49; 1,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,36; 2,02</t>
+          <t>-5,61; 1,56</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 229,81</t>
+          <t>-43,46; 255,81</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-71,3; 131,99</t>
+          <t>-67,99; 124,8</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,25; 125,33</t>
+          <t>-75,19; 124,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,9; 256,68</t>
+          <t>-57,55; 196,52</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-81,03; 87,08</t>
+          <t>-83,26; 95,81</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-80,11; 100,32</t>
+          <t>-78,96; 91,21</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,49; 145,81</t>
+          <t>-36,03; 136,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-61,97; 61,48</t>
+          <t>-65,45; 40,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-64,32; 51,29</t>
+          <t>-66,41; 39,63</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 16,13</t>
+          <t>2,76; 16,83</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 10,43</t>
+          <t>-2,04; 10,63</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 9,5</t>
+          <t>-3,06; 9,44</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,02; 6,45</t>
+          <t>-8,82; 6,42</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -0,39</t>
+          <t>-12,81; -0,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,52; -2,51</t>
+          <t>-14,65; -2,54</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 9,06</t>
+          <t>-1,52; 9,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 3,25</t>
+          <t>-5,77; 3,56</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 0,7</t>
+          <t>-7,38; 0,95</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,0; —</t>
+          <t>-18,64; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-70,65; —</t>
+          <t>-68,08; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-69,22; 142,83</t>
+          <t>-72,14; 167,73</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,94</t>
+          <t>-100,0; 36,35</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; -0,32</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-25,97; 236,74</t>
+          <t>-19,55; 260,08</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-70,16; 113,25</t>
+          <t>-68,49; 109,72</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,39; 24,74</t>
+          <t>-85,48; 37,74</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 10,17</t>
+          <t>-7,71; 9,46</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 4,24</t>
+          <t>-9,29; 4,15</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 14,5</t>
+          <t>-6,26; 14,33</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,1; 6,93</t>
+          <t>-11,03; 7,18</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 21,73</t>
+          <t>-4,77; 20,13</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,58; 6,4</t>
+          <t>-12,37; 6,17</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 5,82</t>
+          <t>-7,06; 5,31</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 9,22</t>
+          <t>-4,13; 9,85</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 6,82</t>
+          <t>-6,06; 7,04</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 384,16</t>
+          <t>-100,0; 441,13</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-57,12; 921,08</t>
+          <t>-54,5; 766,08</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-77,11; 217,86</t>
+          <t>-82,47; 195,84</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-62,59; 320,03</t>
+          <t>-54,9; 366,67</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,27; 290,56</t>
+          <t>-75,52; 344,73</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 4,08</t>
+          <t>-1,72; 4,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 2,71</t>
+          <t>-2,67; 2,78</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,21; 2,35</t>
+          <t>-3,04; 2,68</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,21</t>
+          <t>-4,18; 1,76</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 0,33</t>
+          <t>-5,43; 0,14</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,37; -1,32</t>
+          <t>-6,35; -1,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 2,04</t>
+          <t>-1,94; 2,28</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,57</t>
+          <t>-3,35; 0,62</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,98; -0,33</t>
+          <t>-4,23; -0,42</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,28; 106,05</t>
+          <t>-27,54; 109,63</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 76,05</t>
+          <t>-41,07; 73,33</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,82; 68,23</t>
+          <t>-46,95; 79,39</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-50,94; 47,12</t>
+          <t>-52,79; 35,4</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-65,34; 8,46</t>
+          <t>-67,78; 3,82</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-76,12; -23,9</t>
+          <t>-75,81; -23,14</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-32,37; 42,62</t>
+          <t>-27,85; 50,12</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-46,39; 11,25</t>
+          <t>-47,72; 13,75</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,25; -5,71</t>
+          <t>-57,93; -5,96</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Clase-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 2,72</t>
+          <t>-8,3; 1,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,62; 8,71</t>
+          <t>-5,74; 8,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 8,49</t>
+          <t>-4,35; 8,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,44; 7,92</t>
+          <t>-5,58; 7,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,62; -1,38</t>
+          <t>-11,27; -1,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,27; 1,77</t>
+          <t>-9,29; 1,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 2,72</t>
+          <t>-5,41; 2,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,71; 1,39</t>
+          <t>-6,42; 1,65</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 3,34</t>
+          <t>-5,04; 3,01</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-62,81; —</t>
+          <t>-68,07; 758,41</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,44; 166,34</t>
+          <t>-87,83; 156,16</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 213,8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-69,62; 195,39</t>
+          <t>-73,03; 200,78</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 3,15</t>
+          <t>-12,17; 3,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-14,3; 0,8</t>
+          <t>-13,29; 1,46</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 0,87</t>
+          <t>-14,83; 0,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,01; -1,75</t>
+          <t>-16,03; -1,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,66; 5,59</t>
+          <t>-10,21; 5,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,89; 1,97</t>
+          <t>-12,83; 1,65</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,25; -0,65</t>
+          <t>-11,11; -0,51</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,66</t>
+          <t>-9,46; 1,31</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,4; -0,6</t>
+          <t>-10,5; -0,11</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,9</t>
+          <t>-100,0; 32,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-89,67; 83,97</t>
+          <t>-87,63; 51,94</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-93,56; 12,72</t>
+          <t>-93,85; 44,39</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-16,67; -1,92</t>
+          <t>-18,32; -1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 17,29</t>
+          <t>-6,5; 16,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; 3,29</t>
+          <t>-12,31; 3,53</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 8,03</t>
+          <t>-8,0; 8,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-9,51; 4,64</t>
+          <t>-10,83; 4,27</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 12,0</t>
+          <t>-7,22; 11,76</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 1,58</t>
+          <t>-9,2; 1,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 7,58</t>
+          <t>-6,02; 7,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 5,68</t>
+          <t>-7,55; 5,28</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-76,47; 895,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1230,32 +1230,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-85,35; 345,71</t>
+          <t>-85,46; 443,92</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 340,19</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 500,89</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-91,91; 68,35</t>
+          <t>-90,08; 80,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-70,54; 249,81</t>
+          <t>-64,61; 205,07</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-84,4; 187,5</t>
+          <t>-85,54; 147,36</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 8,98</t>
+          <t>-3,77; 8,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 4,02</t>
+          <t>-6,0; 4,37</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 3,76</t>
+          <t>-6,7; 3,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 7,1</t>
+          <t>-4,82; 7,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,99; 2,6</t>
+          <t>-7,59; 1,96</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,36; 2,61</t>
+          <t>-7,51; 2,72</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,83; 6,05</t>
+          <t>-2,55; 6,34</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,49; 1,65</t>
+          <t>-5,08; 1,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 1,56</t>
+          <t>-5,47; 1,87</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-43,46; 255,81</t>
+          <t>-47,55; 266,94</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,99; 124,8</t>
+          <t>-67,15; 141,63</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,19; 124,79</t>
+          <t>-75,57; 132,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-57,55; 196,52</t>
+          <t>-60,33; 238,55</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,26; 95,81</t>
+          <t>-83,18; 87,22</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,96; 91,21</t>
+          <t>-78,88; 91,52</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-36,03; 136,38</t>
+          <t>-32,19; 144,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-65,45; 40,48</t>
+          <t>-62,89; 50,6</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-66,41; 39,63</t>
+          <t>-65,53; 51,49</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,76; 16,83</t>
+          <t>2,47; 16,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 10,63</t>
+          <t>-2,28; 10,18</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,06; 9,44</t>
+          <t>-3,47; 9,34</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,82; 6,42</t>
+          <t>-8,35; 6,89</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -0,51</t>
+          <t>-13,14; -0,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,65; -2,54</t>
+          <t>-14,42; -2,68</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 9,19</t>
+          <t>-1,16; 10,26</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 3,56</t>
+          <t>-6,27; 3,1</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 0,95</t>
+          <t>-7,37; 0,85</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-18,64; —</t>
+          <t>-0,67; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-68,08; —</t>
+          <t>-58,21; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-72,14; 167,73</t>
+          <t>-71,04; 174,36</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 36,35</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; -13,6</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 260,08</t>
+          <t>-21,53; 259,48</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-68,49; 109,72</t>
+          <t>-72,54; 98,71</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-85,48; 37,74</t>
+          <t>-82,08; 32,67</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 9,46</t>
+          <t>-7,46; 10,22</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 4,15</t>
+          <t>-10,13; 4,08</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 14,33</t>
+          <t>-6,14; 14,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-11,03; 7,18</t>
+          <t>-12,41; 6,66</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 20,13</t>
+          <t>-4,57; 19,98</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,37; 6,17</t>
+          <t>-12,41; 5,85</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-7,06; 5,31</t>
+          <t>-6,73; 5,88</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 9,85</t>
+          <t>-4,96; 9,8</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,06; 7,04</t>
+          <t>-6,68; 7,2</t>
         </is>
       </c>
     </row>
@@ -1878,12 +1878,12 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 441,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-54,5; 766,08</t>
+          <t>-58,87; 714,29</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-82,47; 195,84</t>
+          <t>-77,91; 254,38</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-54,9; 366,67</t>
+          <t>-59,33; 327,75</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-75,52; 344,73</t>
+          <t>-83,05; 280,58</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 4,21</t>
+          <t>-1,78; 4,04</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,67; 2,78</t>
+          <t>-3,11; 2,67</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,68</t>
+          <t>-3,11; 2,33</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 1,76</t>
+          <t>-3,86; 2,09</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 0,14</t>
+          <t>-5,53; 0,16</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,35; -1,25</t>
+          <t>-6,39; -1,25</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 2,28</t>
+          <t>-2,05; 2,08</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 0,62</t>
+          <t>-3,14; 0,66</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,23; -0,42</t>
+          <t>-4,01; -0,27</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,54; 109,63</t>
+          <t>-27,39; 109,69</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-41,07; 73,33</t>
+          <t>-46,02; 72,65</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-46,95; 79,39</t>
+          <t>-47,8; 63,66</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-52,79; 35,4</t>
+          <t>-49,57; 43,73</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-67,78; 3,82</t>
+          <t>-68,29; 5,43</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-75,81; -23,14</t>
+          <t>-76,82; -22,2</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-27,85; 50,12</t>
+          <t>-30,23; 42,02</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-47,72; 13,75</t>
+          <t>-46,36; 12,76</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-57,93; -5,96</t>
+          <t>-56,61; -4,55</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP19C04-Clase-trans_camb.xlsx
+++ b/data/trans_camb/IP19C04-Clase-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,32</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-4,23</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,24</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,43</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,04</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,19</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,32</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-4,23</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-2,44</t>
+          <t>1,89</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,42</t>
+          <t>-0,38</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-8,3; 1,93</t>
+          <t>-5,57; 8,05</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 8,68</t>
+          <t>-11,26; -1,37</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,35; 8,2</t>
+          <t>-8,94; 2,17</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 7,82</t>
+          <t>-7,68; 2,61</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-11,27; -1,37</t>
+          <t>-6,02; 8,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 1,82</t>
+          <t>-4,18; 7,66</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 2,46</t>
+          <t>-5,72; 3,01</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 1,65</t>
+          <t>-6,38; 1,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 3,01</t>
+          <t>-4,64; 3,32</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-53,0%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-63,4%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57,32%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,64%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-57,6%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,38%</t>
+          <t>-9,57%</t>
         </is>
       </c>
     </row>
@@ -793,7 +793,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-68,07; 758,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-67,64; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-87,83; 156,16</t>
+          <t>-86,73; 232,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 213,8</t>
+          <t>-100,0; 198,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-73,03; 200,78</t>
+          <t>-72,12; 186,52</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-5,88</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,7</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-4,09</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>-3,69</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>-4,62</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-5,21</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-5,88</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,7</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-3,74</t>
+          <t>-5,22</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-4,49</t>
+          <t>-4,67</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 3,34</t>
+          <t>-15,35; -1,75</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-13,29; 1,46</t>
+          <t>-10,74; 5,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 0,17</t>
+          <t>-13,55; 0,94</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-16,03; -1,75</t>
+          <t>-11,97; 3,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,21; 5,55</t>
+          <t>-13,79; 1,22</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,83; 1,65</t>
+          <t>-14,3; 0,05</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-11,11; -0,51</t>
+          <t>-10,76; -0,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,46; 1,31</t>
+          <t>-9,02; 1,6</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-10,5; -0,11</t>
+          <t>-10,4; -0,47</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-100,0%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-28,86%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-69,52%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>-53,1%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>-66,53%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-74,91%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-28,86%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-63,69%</t>
+          <t>-75,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-69,68%</t>
+          <t>-72,61%</t>
         </is>
       </c>
     </row>
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 32,84</t>
+          <t>-100,0; 32,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 51,94</t>
+          <t>-87,66; 79,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-93,85; 44,39</t>
+          <t>-94,63; -0,59</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-0,24</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-2,95</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-0,14</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-6,18</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>4,44</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-3,62</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,24</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-2,95</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,23</t>
+          <t>-3,59</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-1,46</t>
+          <t>-1,75</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,32; -1,86</t>
+          <t>-7,93; 9,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,5; 16,82</t>
+          <t>-9,8; 4,72</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-12,31; 3,53</t>
+          <t>-7,62; 10,27</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 8,86</t>
+          <t>-16,38; -1,84</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 4,27</t>
+          <t>-4,67; 16,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 11,76</t>
+          <t>-12,1; 4,19</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 1,87</t>
+          <t>-9,11; 1,73</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 7,51</t>
+          <t>-5,84; 7,39</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 5,28</t>
+          <t>-7,75; 4,52</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-3,57%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-44,46%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-2,12%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>71,77%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-58,5%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-3,57%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-44,46%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>-58,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-22,63%</t>
+          <t>-27,02%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>-81,55; 414,08</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 298,27</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-100,0; 462,32</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>-79,6; —</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-85,46; 443,92</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 500,89</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-90,08; 80,63</t>
+          <t>-88,24; 155,51</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-64,61; 205,07</t>
+          <t>-65,12; 219,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-85,54; 147,36</t>
+          <t>-86,39; 173,65</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-2,41</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-2,33</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>2,44</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>-0,7</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,35</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>0,9</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-2,41</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-2,07</t>
+          <t>-1,0</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-1,73</t>
+          <t>-1,7</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,77; 8,66</t>
+          <t>-5,0; 6,92</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 4,37</t>
+          <t>-7,8; 2,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-6,7; 3,49</t>
+          <t>-7,59; 2,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 7,67</t>
+          <t>-3,71; 8,91</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 1,96</t>
+          <t>-6,68; 4,38</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,51; 2,72</t>
+          <t>-6,3; 4,01</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 6,34</t>
+          <t>-2,57; 5,96</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-5,08; 1,97</t>
+          <t>-5,38; 2,27</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-5,47; 1,87</t>
+          <t>-5,34; 2,07</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>14,32%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-38,43%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-37,18%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>39,1%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>-11,27%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-21,65%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>14,32%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-38,43%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-32,96%</t>
+          <t>-16,06%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-27,69%</t>
+          <t>-27,24%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-47,55; 266,94</t>
+          <t>-56,9; 256,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-67,15; 141,63</t>
+          <t>-81,03; 87,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-75,57; 132,28</t>
+          <t>-81,28; 96,09</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-60,33; 238,55</t>
+          <t>-47,05; 229,81</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-83,18; 87,22</t>
+          <t>-71,3; 131,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-78,88; 91,52</t>
+          <t>-74,17; 130,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-32,19; 144,86</t>
+          <t>-32,49; 145,81</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-62,89; 50,6</t>
+          <t>-61,97; 61,48</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-65,53; 51,49</t>
+          <t>-64,61; 55,09</t>
         </is>
       </c>
     </row>
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>-1,19</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-6,24</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>-7,26</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>9,52</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>4,01</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>3,04</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-1,19</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>-6,24</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-7,31</t>
+          <t>3,37</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-2,96</t>
+          <t>-2,67</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,47; 16,43</t>
+          <t>-8,02; 6,45</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 10,18</t>
+          <t>-12,81; -0,39</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,47; 9,34</t>
+          <t>-14,42; -2,41</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 6,89</t>
+          <t>2,26; 16,13</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -0,69</t>
+          <t>-2,08; 10,43</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-14,42; -2,68</t>
+          <t>-3,13; 10,33</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-1,16; 10,26</t>
+          <t>-1,69; 9,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,27; 3,1</t>
+          <t>-5,84; 3,25</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-7,37; 0,85</t>
+          <t>-6,81; 1,22</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>-14,04%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-73,53%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>-85,52%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>334,62%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>140,81%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>106,66%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-14,04%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>-73,53%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-86,03%</t>
+          <t>118,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-49,16%</t>
+          <t>-44,45%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-0,67; —</t>
+          <t>-69,22; 142,83</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-58,21; —</t>
+          <t>-100,0; 29,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 14,42</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>-9,0; —</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>-70,65; —</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>-71,04; 174,36</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; -13,6</t>
-        </is>
-      </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-21,53; 259,48</t>
+          <t>-25,97; 236,74</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 98,71</t>
+          <t>-70,16; 113,25</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-82,08; 32,67</t>
+          <t>-80,98; 38,38</t>
         </is>
       </c>
     </row>
@@ -1704,32 +1704,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-1,9</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>6,78</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>-2,98</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
           <t>0,23</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr">
         <is>
           <t>-2,69</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>1,41</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>-1,9</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>6,78</t>
-        </is>
-      </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-3,17</t>
+          <t>-2,17</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-0,8</t>
+          <t>-2,54</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-7,46; 10,22</t>
+          <t>-11,1; 6,93</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-10,13; 4,08</t>
+          <t>-4,16; 21,73</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-6,14; 14,17</t>
+          <t>-12,58; 6,87</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 6,66</t>
+          <t>-7,82; 10,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 19,98</t>
+          <t>-9,61; 4,24</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-12,41; 5,85</t>
+          <t>-9,46; 2,8</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 5,88</t>
+          <t>-6,79; 5,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>-4,96; 9,8</t>
+          <t>-5,17; 9,22</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-6,68; 7,2</t>
+          <t>-8,31; 2,38</t>
         </is>
       </c>
     </row>
@@ -1810,32 +1810,32 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-26,38%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>93,96%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>-41,31%</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
           <t>4,89%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>-56,1%</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>29,47%</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>-26,38%</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>93,96%</t>
-        </is>
-      </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-43,96%</t>
+          <t>-45,11%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-13,51%</t>
+          <t>-42,7%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 384,16</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>-57,12; 921,08</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>-58,87; 714,29</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-77,91; 254,38</t>
+          <t>-77,11; 217,86</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>-59,33; 327,75</t>
+          <t>-62,59; 320,03</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-83,05; 280,58</t>
+          <t>-91,9; 96,46</t>
         </is>
       </c>
     </row>
@@ -1920,32 +1920,32 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-1,06</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-2,62</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>-3,66</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
           <t>1,26</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr">
         <is>
           <t>0,05</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-0,41</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>-1,06</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>-2,62</t>
-        </is>
-      </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-3,6</t>
+          <t>-0,76</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>-2,12</t>
+          <t>-2,29</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 4,04</t>
+          <t>-4,12; 2,21</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,67</t>
+          <t>-5,3; 0,33</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 2,33</t>
+          <t>-6,51; -1,42</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 2,09</t>
+          <t>-1,8; 4,08</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-5,53; 0,16</t>
+          <t>-2,7; 2,71</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-6,39; -1,25</t>
+          <t>-3,46; 1,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 2,08</t>
+          <t>-2,24; 2,04</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 0,66</t>
+          <t>-3,3; 0,57</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-4,01; -0,27</t>
+          <t>-4,11; -0,57</t>
         </is>
       </c>
     </row>
@@ -2026,32 +2026,32 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-16,22%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-39,96%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>-55,96%</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
           <t>24,38%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr">
         <is>
           <t>0,92%</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-7,95%</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>-16,22%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>-39,96%</t>
-        </is>
-      </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-54,98%</t>
+          <t>-14,7%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>-36,09%</t>
+          <t>-38,96%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-27,39; 109,69</t>
+          <t>-50,94; 47,12</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-46,02; 72,65</t>
+          <t>-65,34; 8,46</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 63,66</t>
+          <t>-76,59; -23,78</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-49,57; 43,73</t>
+          <t>-30,28; 106,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-68,29; 5,43</t>
+          <t>-43,24; 76,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-76,82; -22,2</t>
+          <t>-50,61; 54,96</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-30,23; 42,02</t>
+          <t>-32,37; 42,62</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 12,76</t>
+          <t>-46,39; 11,25</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-56,61; -4,55</t>
+          <t>-59,21; -11,79</t>
         </is>
       </c>
     </row>
